--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41817F3A-FAAD-42DA-A541-E51B46C937AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517A35C-8FB9-49CF-81C5-31060E9D96FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -132,10 +132,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>楚恭王</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>世子</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -355,6 +351,10 @@
   </si>
   <si>
     <t>005治疗成功</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>楚王</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -862,37 +862,37 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>28</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>34</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>29</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>35</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="M1" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>32</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>33</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>15</v>
@@ -903,13 +903,13 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -920,7 +920,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1053,22 +1053,22 @@
         <v>6</v>
       </c>
       <c r="C2" s="12" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>25</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>27</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1086,11 +1086,11 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1101,18 +1101,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1130,11 +1130,11 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1145,18 +1145,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>40</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>41</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1174,11 +1174,11 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1189,18 +1189,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1211,18 +1211,18 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1230,17 +1230,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6517A35C-8FB9-49CF-81C5-31060E9D96FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347D43B3-20BD-49C3-8753-057066054AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -137,42 +137,6 @@
   </si>
   <si>
     <t>父王，我觉得好多了</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <r>
-      <t>世子所患的</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>时</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="3"/>
-        <charset val="128"/>
-      </rPr>
-      <t>脾虚湿盛</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Microsoft YaHei"/>
-        <family val="3"/>
-        <charset val="134"/>
-      </rPr>
-      <t>之证，只要按方每日吃药，病情就无大碍了。</t>
-    </r>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -278,10 +242,6 @@
       </rPr>
       <t>无以为报。这一千两白银是我的一点心意，感谢先生救命之恩。</t>
     </r>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>世子乃人中龙凤，可天下人只要来看病，草民眼里看到的就只有病人。十文是诊费，绝非世子命价。</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -355,6 +315,26 @@
   </si>
   <si>
     <t>楚王</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <r>
+      <t>世子所患的是脾虚湿盛</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Microsoft YaHei"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t>之证，只要按方每日吃药，病情就无大碍了。</t>
+    </r>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世子乃人中龙凤，但无论何人前来看病，草民眼里看到的都只有病人。十文是诊费，绝非世子命价。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -862,37 +842,37 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>27</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>33</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>34</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="M1" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>31</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>32</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>15</v>
@@ -903,13 +883,13 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -920,7 +900,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1059,13 +1039,13 @@
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>26</v>
-      </c>
       <c r="G2" s="2" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>22</v>
@@ -1086,11 +1066,11 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1101,18 +1081,18 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1130,11 +1110,11 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1145,18 +1125,18 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>39</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>40</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1174,11 +1154,11 @@
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1189,18 +1169,18 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1211,18 +1191,18 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1230,17 +1210,17 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{347D43B3-20BD-49C3-8753-057066054AA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCBEBAC-34A2-4411-9557-BC8D7E6ECD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -187,10 +187,6 @@
   </si>
   <si>
     <t>subtitle</t>
-  </si>
-  <si>
-    <t>名声+1000</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>草民行医只取诊费十文，这一千两小人不能收。</t>
@@ -335,6 +331,10 @@
   </si>
   <si>
     <t>世子乃人中龙凤，但无论何人前来看病，草民眼里看到的都只有病人。十文是诊费，绝非世子命价。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>名望+1000</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -863,7 +863,7 @@
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="L1" s="19" t="s">
         <v>26</v>
@@ -886,7 +886,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>28</v>
@@ -900,7 +900,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -1045,7 +1045,7 @@
         <v>25</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>22</v>
@@ -1070,7 +1070,7 @@
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1081,7 +1081,7 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>9</v>
@@ -1092,7 +1092,7 @@
       </c>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1125,10 +1125,10 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>38</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>39</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8" t="s">
@@ -1136,7 +1136,7 @@
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1169,7 +1169,7 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>9</v>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1191,7 +1191,7 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>9</v>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>36</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BCBEBAC-34A2-4411-9557-BC8D7E6ECD28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695F4ADC-17EB-4B1B-9BD5-DA17C1BB43CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,23 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
   <si>
     <t>StoryID</t>
   </si>
@@ -145,10 +134,6 @@
   </si>
   <si>
     <t>after</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>dim</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -346,7 +331,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -360,7 +345,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -381,7 +366,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -532,7 +517,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -811,24 +796,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.86328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -842,37 +827,37 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>32</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>27</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>33</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="M1" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>30</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>31</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>15</v>
@@ -886,10 +871,10 @@
         <v>23</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -900,7 +885,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -988,14 +973,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1041,11 +1026,9 @@
       <c r="E2" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="H2" s="12" t="s">
         <v>22</v>
@@ -1065,12 +1048,10 @@
         <v>8</v>
       </c>
       <c r="E3" s="2"/>
-      <c r="F3" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1081,18 +1062,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E4" s="2"/>
-      <c r="F4" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1109,12 +1088,10 @@
         <v>8</v>
       </c>
       <c r="E5" s="2"/>
-      <c r="F5" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1125,18 +1102,16 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>38</v>
+        <v>36</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>9</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="F6" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F6" s="8"/>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1153,12 +1128,10 @@
         <v>8</v>
       </c>
       <c r="E7" s="2"/>
-      <c r="F7" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1169,18 +1142,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E8" s="2"/>
-      <c r="F8" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F8" s="8"/>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1191,18 +1162,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="E9" s="2"/>
-      <c r="F9" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1210,17 +1179,15 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
-      <c r="F10" s="8" t="s">
-        <v>25</v>
-      </c>
+      <c r="F10" s="8"/>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{695F4ADC-17EB-4B1B-9BD5-DA17C1BB43CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E45035-6D0E-4158-8566-787E07A85613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -20,6 +20,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -125,10 +136,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>父王，我觉得好多了</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>005_02</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -174,19 +181,11 @@
     <t>subtitle</t>
   </si>
   <si>
-    <t>草民行医只取诊费十文，这一千两小人不能收。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>陈皮</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
     <t>mid</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>少掌柜的那可是一千两白银啊！</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -315,11 +314,23 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>世子乃人中龙凤，但无论何人前来看病，草民眼里看到的都只有病人。十文是诊费，绝非世子命价。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>名望+1000</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>父王，我觉得好多了。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>少掌柜的，那可是一千两白银啊！</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>一千两太多了，草民不能收。</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治病人，王爷只需付200文诊费即可。</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -331,7 +342,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -345,7 +356,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -366,7 +377,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -517,7 +528,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -796,24 +807,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="8.73046875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.3984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.86328125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.59765625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.265625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.86328125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.3984375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.59765625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.46484375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.86328125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.1328125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.73046875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.86328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -827,37 +838,37 @@
         <v>13</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="15" t="s">
         <v>31</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>26</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>32</v>
       </c>
       <c r="J1" s="16" t="s">
         <v>14</v>
       </c>
       <c r="K1" s="16" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="L1" s="19" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="M1" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="N1" s="19" t="s">
         <v>29</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>30</v>
       </c>
       <c r="O1" s="18" t="s">
         <v>15</v>
@@ -868,13 +879,13 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" s="5" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B2" s="12" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>19</v>
@@ -885,7 +896,7 @@
       <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="5" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="I2" s="1"/>
       <c r="J2" s="1"/>
@@ -973,14 +984,14 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
@@ -1024,14 +1035,14 @@
         <v>9</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="H2" s="12" t="s">
-        <v>22</v>
+        <v>46</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1051,7 +1062,7 @@
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1062,16 +1073,16 @@
         <v>6</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1091,7 +1102,7 @@
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
       <c r="H5" s="12" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1102,7 +1113,7 @@
         <v>6</v>
       </c>
       <c r="C6" s="12" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>9</v>
@@ -1111,7 +1122,7 @@
       <c r="F6" s="8"/>
       <c r="G6" s="3"/>
       <c r="H6" s="13" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1131,7 +1142,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1142,16 +1153,16 @@
         <v>6</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8"/>
       <c r="G8" s="3"/>
       <c r="H8" s="13" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1162,16 +1173,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
       <c r="H9" s="13" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1179,7 +1190,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
@@ -1187,7 +1198,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:8">

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3E45035-6D0E-4158-8566-787E07A85613}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE976DB-CFD0-4691-9ADE-3F56B65FF698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-20610" yWindow="3210" windowWidth="20730" windowHeight="11040" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,26 +21,12 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="50">
-  <si>
-    <t>StoryID</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
   <si>
     <t>LineIndex</t>
   </si>
@@ -80,30 +66,13 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>StoryName</t>
-  </si>
-  <si>
-    <t>TriggerType</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>NpcID</t>
-  </si>
-  <si>
     <t>PlayOnce</t>
   </si>
   <si>
-    <t>ReturnScene</t>
-  </si>
-  <si>
     <t>SortIndex</t>
   </si>
   <si>
     <t>night</t>
-  </si>
-  <si>
-    <t>night</t>
-    <phoneticPr fontId="2"/>
   </si>
   <si>
     <r>
@@ -144,40 +113,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>ClinicNpcPortraitPath</t>
-  </si>
-  <si>
-    <t>TriggerStoryID</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>story_npc_cured</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerScene</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Reputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>Experience</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerReputation</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerEntryId</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>TriggerDay</t>
-  </si>
-  <si>
     <t>subtitle</t>
   </si>
   <si>
@@ -240,10 +175,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>Disease</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <t>res://Assets/Background/00</t>
     </r>
@@ -333,16 +264,104 @@
     <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治病人，王爷只需付200文诊费即可。</t>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>剧情名</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发场景</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发天数</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <r>
+      <t>金</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>钱判定</t>
+    </r>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>名望判定</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发条目</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发剧情ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>触发治疗结果</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>播放后</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物ID</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>疾病</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>人物立绘路径</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励金钱</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励名望</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>奖励心得</t>
+    <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>cured</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -356,7 +375,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -377,7 +396,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="游ゴシック"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -406,13 +425,27 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -427,20 +460,22 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FF92D050"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
+        <fgColor rgb="FFFF0000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF200"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF00B0F0"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -471,7 +506,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -497,9 +532,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -515,20 +547,43 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -806,175 +861,200 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
-  <dimension ref="A1:P20"/>
-  <sheetFormatPr defaultRowHeight="18.75"/>
+  <dimension ref="A1:T20"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="8.75" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15.625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="7.375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.5" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.875" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="10.75" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
-      <c r="A1" s="9" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="6" t="s">
+    <row r="1" spans="1:20" s="22" customFormat="1">
+      <c r="A1" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="B1" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C1" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="D1" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>38</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="J1" s="18" t="s">
+        <v>43</v>
+      </c>
+      <c r="K1" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="M1" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="N1" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="O1" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="P1" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q1" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="R1" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="S1" s="21" t="s">
+        <v>11</v>
+      </c>
+      <c r="T1" s="21" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:20" s="22" customFormat="1">
+      <c r="A2" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="L2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="G1" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="H1" s="15" t="s">
-        <v>25</v>
-      </c>
-      <c r="I1" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="L1" s="19" t="s">
-        <v>24</v>
-      </c>
-      <c r="M1" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="N1" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="O1" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" s="18" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16">
-      <c r="A2" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2">
+      <c r="M2" s="23"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="2">
         <v>1000</v>
       </c>
-      <c r="N2" s="2">
-        <v>5</v>
-      </c>
-      <c r="O2" s="1" t="b">
+      <c r="R2" s="25"/>
+      <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
-      <c r="P2" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
-      <c r="C3" s="10"/>
-      <c r="H3" s="17"/>
-      <c r="O3" s="11"/>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="C4" s="10"/>
-      <c r="H4" s="17"/>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="C5" s="10"/>
-      <c r="H5" s="17"/>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="H6" s="17"/>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="H7" s="17"/>
-    </row>
-    <row r="8" spans="1:16">
-      <c r="H8" s="17"/>
-    </row>
-    <row r="9" spans="1:16">
-      <c r="H9" s="17"/>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="H10" s="17"/>
-    </row>
-    <row r="11" spans="1:16">
-      <c r="H11" s="17"/>
-    </row>
-    <row r="12" spans="1:16">
-      <c r="H12" s="17"/>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="H13" s="17"/>
-    </row>
-    <row r="14" spans="1:16">
-      <c r="H14" s="17"/>
-    </row>
-    <row r="15" spans="1:16">
-      <c r="H15" s="17"/>
-    </row>
-    <row r="16" spans="1:16">
-      <c r="H16" s="17"/>
+      <c r="T2" s="25"/>
+    </row>
+    <row r="3" spans="1:20">
+      <c r="C3" s="9"/>
+      <c r="H3" s="14"/>
+      <c r="O3" s="10"/>
+    </row>
+    <row r="4" spans="1:20">
+      <c r="C4" s="9"/>
+      <c r="H4" s="14"/>
+    </row>
+    <row r="5" spans="1:20">
+      <c r="C5" s="9"/>
+      <c r="H5" s="14"/>
+    </row>
+    <row r="6" spans="1:20">
+      <c r="H6" s="14"/>
+    </row>
+    <row r="7" spans="1:20">
+      <c r="H7" s="14"/>
+    </row>
+    <row r="8" spans="1:20">
+      <c r="H8" s="14"/>
+    </row>
+    <row r="9" spans="1:20">
+      <c r="H9" s="14"/>
+    </row>
+    <row r="10" spans="1:20">
+      <c r="H10" s="14"/>
+    </row>
+    <row r="11" spans="1:20">
+      <c r="H11" s="14"/>
+    </row>
+    <row r="12" spans="1:20">
+      <c r="H12" s="14"/>
+    </row>
+    <row r="13" spans="1:20">
+      <c r="H13" s="14"/>
+    </row>
+    <row r="14" spans="1:20">
+      <c r="H14" s="14"/>
+    </row>
+    <row r="15" spans="1:20">
+      <c r="H15" s="14"/>
+    </row>
+    <row r="16" spans="1:20">
+      <c r="H16" s="14"/>
     </row>
     <row r="17" spans="8:8">
-      <c r="H17" s="17"/>
+      <c r="H17" s="14"/>
     </row>
     <row r="18" spans="8:8">
-      <c r="H18" s="17"/>
+      <c r="H18" s="14"/>
     </row>
     <row r="19" spans="8:8">
-      <c r="H19" s="17"/>
+      <c r="H19" s="14"/>
     </row>
     <row r="20" spans="8:8">
-      <c r="H20" s="17"/>
+      <c r="H20" s="14"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>
+  <dataValidations count="5">
+    <dataValidation type="list" sqref="C2" xr:uid="{6EDC359C-38EB-4DE0-9126-8A0F9E039AE9}">
+      <formula1>"clinic,night,night_end"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="E2 G2" xr:uid="{588C0938-7EE0-4563-AFCB-9DABED5389FE}">
+      <formula1>"≥,≤"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="L2" xr:uid="{8583F18F-BB80-4037-8354-F930C19A7879}">
+      <formula1>"clinic,night,end_game"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="S2" xr:uid="{EC543E9B-9E76-41A9-BC83-33F6DC304502}">
+      <formula1>"TRUE,FALSE"</formula1>
+    </dataValidation>
+    <dataValidation type="list" sqref="K2" xr:uid="{AC1723F2-3451-472F-AE6D-E528E1AB57DD}">
+      <formula1>"cured,failed"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -984,41 +1064,41 @@
   <dimension ref="A1:H24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="D1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="E1" s="7" t="s">
+      <c r="F1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="H1" s="6" t="s">
         <v>4</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:8">
@@ -1026,23 +1106,23 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>21</v>
+        <v>5</v>
+      </c>
+      <c r="C2" s="11" t="s">
+        <v>15</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="F2" s="8"/>
       <c r="G2" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>46</v>
+        <v>25</v>
+      </c>
+      <c r="H2" s="11" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1050,19 +1130,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E3" s="2"/>
       <c r="F3" s="8"/>
       <c r="G3" s="2"/>
       <c r="H3" s="1" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1070,19 +1150,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E4" s="2"/>
       <c r="F4" s="8"/>
       <c r="G4" s="2"/>
       <c r="H4" s="1" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1090,19 +1170,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" s="2"/>
       <c r="F5" s="8"/>
       <c r="G5" s="2"/>
-      <c r="H5" s="12" t="s">
-        <v>48</v>
+      <c r="H5" s="11" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1110,19 +1190,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>34</v>
+        <v>5</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>19</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E6" s="3"/>
       <c r="F6" s="8"/>
       <c r="G6" s="3"/>
-      <c r="H6" s="13" t="s">
-        <v>47</v>
+      <c r="H6" s="12" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1130,19 +1210,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="D7" s="8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>49</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1150,19 +1230,19 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="8"/>
       <c r="G8" s="3"/>
-      <c r="H8" s="13" t="s">
-        <v>37</v>
+      <c r="H8" s="12" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1170,19 +1250,19 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="8"/>
       <c r="G9" s="3"/>
-      <c r="H9" s="13" t="s">
-        <v>38</v>
+      <c r="H9" s="12" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="10" spans="1:8">
@@ -1190,7 +1270,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="2"/>
@@ -1198,7 +1278,7 @@
       <c r="F10" s="8"/>
       <c r="G10" s="2"/>
       <c r="H10" s="8" t="s">
-        <v>45</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:8">
@@ -1254,12 +1334,12 @@
         <v>14</v>
       </c>
       <c r="B15" s="1"/>
-      <c r="C15" s="12"/>
+      <c r="C15" s="11"/>
       <c r="D15" s="2"/>
       <c r="E15" s="3"/>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="13"/>
+      <c r="H15" s="12"/>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="1">
@@ -1271,17 +1351,17 @@
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="13"/>
+      <c r="H16" s="12"/>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="12"/>
+      <c r="C17" s="11"/>
       <c r="D17" s="2"/>
       <c r="E17" s="3"/>
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
-      <c r="H17" s="14"/>
+      <c r="H17" s="13"/>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="3"/>

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Doctor\DataTables\DetailText\剧情\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE976DB-CFD0-4691-9ADE-3F56B65FF698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364CAE34-EDBB-4DAF-8BCD-3572CAB83275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3308" yWindow="3308" windowWidth="21600" windowHeight="11422" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -21,12 +21,23 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="55">
   <si>
     <t>LineIndex</t>
   </si>
@@ -352,6 +363,14 @@
   <si>
     <t>cured</t>
   </si>
+  <si>
+    <t>q</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>Music</t>
+    <phoneticPr fontId="10"/>
+  </si>
 </sst>
 </file>
 
@@ -361,7 +380,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -375,7 +394,7 @@
     </font>
     <font>
       <sz val="6"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="128"/>
       <scheme val="minor"/>
@@ -396,7 +415,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="游ゴシック"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -506,7 +525,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -581,9 +600,12 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -862,25 +884,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34F23D77-4900-4189-9994-325381E620A7}">
   <dimension ref="A1:T20"/>
-  <sheetFormatPr defaultRowHeight="18"/>
+  <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="1" max="1" width="7.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.46484375" bestFit="1" customWidth="1"/>
-    <col min="3" max="7" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="8.9296875" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.06640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="7" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="8.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.125" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="13" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="7" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="5.06640625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="5.125" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="13" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="8.9296875" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.19921875" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10.73046875" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="8.875" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.25" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="10.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="22" customFormat="1">
+    <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
         <v>34</v>
       </c>
@@ -942,7 +964,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" spans="1:20" s="22" customFormat="1">
+    <row r="2" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A2" s="5" t="s">
         <v>16</v>
       </c>
@@ -972,7 +994,9 @@
       <c r="Q2" s="2">
         <v>1000</v>
       </c>
-      <c r="R2" s="25"/>
+      <c r="R2" s="25">
+        <v>5</v>
+      </c>
       <c r="S2" s="25" t="b">
         <v>1</v>
       </c>
@@ -993,6 +1017,9 @@
     </row>
     <row r="6" spans="1:20">
       <c r="H6" s="14"/>
+      <c r="P6" s="22" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="7" spans="1:20">
       <c r="H7" s="14"/>
@@ -1061,21 +1088,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2737C09-A8AE-40CE-8CCF-722F07DBFAAF}">
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:I24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="11.265625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.46484375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.3984375" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.59765625" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.86328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="6.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.1328125" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="91.86328125" style="4" customWidth="1"/>
+    <col min="1" max="1" width="11.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.375" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="6.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="91.875" style="4" customWidth="1"/>
     <col min="9" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="6" t="s">
         <v>0</v>
       </c>
@@ -1100,8 +1127,11 @@
       <c r="H1" s="6" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" s="26" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -1124,8 +1154,9 @@
       <c r="H2" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="3" spans="1:8">
+      <c r="I2" s="1"/>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -1144,8 +1175,9 @@
       <c r="H3" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="4" spans="1:8">
+      <c r="I3" s="1"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1164,8 +1196,9 @@
       <c r="H4" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" s="1"/>
+    </row>
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1184,8 +1217,9 @@
       <c r="H5" s="11" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:8">
+      <c r="I5" s="1"/>
+    </row>
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1204,8 +1238,9 @@
       <c r="H6" s="12" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="7" spans="1:8">
+      <c r="I6" s="1"/>
+    </row>
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1224,8 +1259,9 @@
       <c r="H7" s="8" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="8" spans="1:8">
+      <c r="I7" s="3"/>
+    </row>
+    <row r="8" spans="1:9">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1244,8 +1280,9 @@
       <c r="H8" s="12" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="I8" s="3"/>
+    </row>
+    <row r="9" spans="1:9">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1264,8 +1301,9 @@
       <c r="H9" s="12" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="10" spans="1:8">
+      <c r="I9" s="3"/>
+    </row>
+    <row r="10" spans="1:9">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1280,8 +1318,9 @@
       <c r="H10" s="8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="11" spans="1:8">
+      <c r="I10" s="3"/>
+    </row>
+    <row r="11" spans="1:9">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1292,8 +1331,9 @@
       <c r="F11" s="3"/>
       <c r="G11" s="3"/>
       <c r="H11" s="3"/>
-    </row>
-    <row r="12" spans="1:8">
+      <c r="I11" s="3"/>
+    </row>
+    <row r="12" spans="1:9">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -1304,8 +1344,9 @@
       <c r="F12" s="3"/>
       <c r="G12" s="3"/>
       <c r="H12" s="3"/>
-    </row>
-    <row r="13" spans="1:8">
+      <c r="I12" s="3"/>
+    </row>
+    <row r="13" spans="1:9">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1316,8 +1357,9 @@
       <c r="F13" s="3"/>
       <c r="G13" s="3"/>
       <c r="H13" s="3"/>
-    </row>
-    <row r="14" spans="1:8">
+      <c r="I13" s="3"/>
+    </row>
+    <row r="14" spans="1:9">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -1328,8 +1370,9 @@
       <c r="F14" s="3"/>
       <c r="G14" s="3"/>
       <c r="H14" s="3"/>
-    </row>
-    <row r="15" spans="1:8">
+      <c r="I14" s="3"/>
+    </row>
+    <row r="15" spans="1:9">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1340,8 +1383,9 @@
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
       <c r="H15" s="12"/>
-    </row>
-    <row r="16" spans="1:8">
+      <c r="I15" s="3"/>
+    </row>
+    <row r="16" spans="1:9">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1352,8 +1396,9 @@
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
       <c r="H16" s="12"/>
-    </row>
-    <row r="17" spans="1:8">
+      <c r="I16" s="3"/>
+    </row>
+    <row r="17" spans="1:9">
       <c r="A17" s="3"/>
       <c r="B17" s="1"/>
       <c r="C17" s="11"/>
@@ -1362,8 +1407,9 @@
       <c r="F17" s="3"/>
       <c r="G17" s="3"/>
       <c r="H17" s="13"/>
-    </row>
-    <row r="18" spans="1:8">
+      <c r="I17" s="3"/>
+    </row>
+    <row r="18" spans="1:9">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1372,8 +1418,9 @@
       <c r="F18" s="3"/>
       <c r="G18" s="3"/>
       <c r="H18" s="3"/>
-    </row>
-    <row r="19" spans="1:8">
+      <c r="I18" s="3"/>
+    </row>
+    <row r="19" spans="1:9">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="3"/>
@@ -1382,8 +1429,9 @@
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
       <c r="H19" s="3"/>
-    </row>
-    <row r="20" spans="1:8">
+      <c r="I19" s="3"/>
+    </row>
+    <row r="20" spans="1:9">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="3"/>
@@ -1392,8 +1440,9 @@
       <c r="F20" s="3"/>
       <c r="G20" s="3"/>
       <c r="H20" s="3"/>
-    </row>
-    <row r="21" spans="1:8">
+      <c r="I20" s="3"/>
+    </row>
+    <row r="21" spans="1:9">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="3"/>
@@ -1402,8 +1451,9 @@
       <c r="F21" s="3"/>
       <c r="G21" s="3"/>
       <c r="H21" s="3"/>
-    </row>
-    <row r="22" spans="1:8">
+      <c r="I21" s="3"/>
+    </row>
+    <row r="22" spans="1:9">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="3"/>
@@ -1412,8 +1462,9 @@
       <c r="F22" s="3"/>
       <c r="G22" s="3"/>
       <c r="H22" s="3"/>
-    </row>
-    <row r="23" spans="1:8">
+      <c r="I22" s="3"/>
+    </row>
+    <row r="23" spans="1:9">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -1422,8 +1473,9 @@
       <c r="F23" s="3"/>
       <c r="G23" s="3"/>
       <c r="H23" s="3"/>
-    </row>
-    <row r="24" spans="1:8">
+      <c r="I23" s="3"/>
+    </row>
+    <row r="24" spans="1:9">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="3"/>
@@ -1432,6 +1484,7 @@
       <c r="F24" s="3"/>
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
+      <c r="I24" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2"/>

--- a/DataTables/DetailText/剧情/005_02治疗成功.xlsx
+++ b/DataTables/DetailText/剧情/005_02治疗成功.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Doctor\DataTables\DetailText\剧情\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{364CAE34-EDBB-4DAF-8BCD-3572CAB83275}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FC35D94-2699-408B-92CA-E175EB0630B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19395" yWindow="5745" windowWidth="16035" windowHeight="8025" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="25440" windowHeight="15270" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Story" sheetId="3" r:id="rId1"/>
@@ -272,10 +272,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治病人，王爷只需付200文诊费即可。</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>剧情ID</t>
     <phoneticPr fontId="10"/>
   </si>
@@ -370,6 +366,10 @@
   <si>
     <t>Music</t>
     <phoneticPr fontId="10"/>
+  </si>
+  <si>
+    <t>世子乃人中龙凤，可草民眼里看到的只有一位需要医治的病人，王爷只需付200文诊费即可。</t>
+    <phoneticPr fontId="2"/>
   </si>
 </sst>
 </file>
@@ -904,58 +904,58 @@
   <sheetData>
     <row r="1" spans="1:20" s="22" customFormat="1" ht="18">
       <c r="A1" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="B1" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="C1" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="C1" s="17" t="s">
+      <c r="D1" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="E1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="F1" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="F1" s="18" t="s">
+      <c r="G1" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="G1" s="18" t="s">
+      <c r="H1" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="H1" s="18" t="s">
+      <c r="I1" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="I1" s="18" t="s">
+      <c r="J1" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="J1" s="18" t="s">
+      <c r="K1" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="K1" s="18" t="s">
+      <c r="L1" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="L1" s="19" t="s">
+      <c r="M1" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="M1" s="20" t="s">
+      <c r="N1" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="O1" s="20" t="s">
         <v>47</v>
       </c>
-      <c r="O1" s="20" t="s">
+      <c r="P1" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="P1" s="20" t="s">
+      <c r="Q1" s="20" t="s">
         <v>49</v>
       </c>
-      <c r="Q1" s="20" t="s">
+      <c r="R1" s="20" t="s">
         <v>50</v>
-      </c>
-      <c r="R1" s="20" t="s">
-        <v>51</v>
       </c>
       <c r="S1" s="21" t="s">
         <v>11</v>
@@ -982,7 +982,7 @@
         <v>24</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L2" s="24" t="s">
         <v>13</v>
@@ -1018,7 +1018,7 @@
     <row r="6" spans="1:20">
       <c r="H6" s="14"/>
       <c r="P6" s="22" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -1128,7 +1128,7 @@
         <v>4</v>
       </c>
       <c r="I1" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -1257,7 +1257,7 @@
       <c r="F7" s="8"/>
       <c r="G7" s="2"/>
       <c r="H7" s="8" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="I7" s="3"/>
     </row>
